--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484228_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484228_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7795</v>
+        <v>5.4611</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0019</v>
+        <v>3.5474</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7776</v>
+        <v>1.9137</v>
       </c>
       <c r="G2" t="n">
         <v>4.5615</v>
@@ -610,13 +610,13 @@
         <v>2.5395</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.09080000000000001</v>
+        <v>0.5908</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5226</v>
+        <v>0.0229</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4318</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2772</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0799</v>
+        <v>3.4974</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2295</v>
+        <v>0.8649</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8504</v>
+        <v>2.6325</v>
       </c>
       <c r="G3" t="n">
         <v>1.2015</v>
@@ -688,13 +688,13 @@
         <v>1.1721</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7063</v>
+        <v>1.1238</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6219</v>
+        <v>0.2573</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0844</v>
+        <v>0.8665</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6104</v>
+        <v>2.9747</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5511</v>
+        <v>0.106</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0593</v>
+        <v>2.8686</v>
       </c>
       <c r="G4" t="n">
         <v>0.753</v>
@@ -766,13 +766,13 @@
         <v>1.1721</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4081</v>
+        <v>0.7724</v>
       </c>
       <c r="T4" t="n">
-        <v>0.864</v>
+        <v>0.419</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5441</v>
+        <v>0.3534</v>
       </c>
       <c r="V4" t="n">
         <v>0.2772</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>A. RECIO PIÑOL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2278</v>
+        <v>2.0133</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7193000000000001</v>
+        <v>-0.8665</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5085</v>
+        <v>2.8798</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7299</v>
+        <v>1.0656</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0289</v>
+        <v>0.715</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7009</v>
+        <v>0.3506</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0944</v>
+        <v>-0.203</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0668</v>
+        <v>0.3901</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0276</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3645</v>
+        <v>1.2687</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0379</v>
+        <v>0.3249</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6733</v>
+        <v>0.9437</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3695</v>
+        <v>0.2482</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1594</v>
+        <v>0.0007</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5289</v>
+        <v>0.2475</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4959</v>
+        <v>-0.2772</v>
       </c>
       <c r="W5" t="n">
-        <v>2.7145</v>
+        <v>-0.6642</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2186</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. RECIO PIÑOL</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.48</v>
+        <v>1.7091</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2909</v>
+        <v>0.7998</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7709</v>
+        <v>0.9093</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0656</v>
+        <v>0.7299</v>
       </c>
       <c r="H6" t="n">
-        <v>0.715</v>
+        <v>0.0289</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3506</v>
+        <v>0.7009</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.203</v>
+        <v>1.0944</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3901</v>
+        <v>1.0668</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.0276</v>
       </c>
       <c r="M6" t="n">
-        <v>1.2687</v>
+        <v>-0.3645</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3249</v>
+        <v>-1.0379</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9437</v>
+        <v>0.6733</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9767</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2851</v>
+        <v>0.8508</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4237</v>
+        <v>-0.079</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1386</v>
+        <v>0.9298</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2772</v>
+        <v>1.4959</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6642</v>
+        <v>2.7145</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3869</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0742</v>
+        <v>0.4217</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1652</v>
+        <v>-1.7199</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2394</v>
+        <v>2.1416</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9486</v>
+        <v>1.0791</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5009</v>
+        <v>1.9417</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5523</v>
+        <v>-0.8626</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0202</v>
+        <v>-0.6635</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6677999999999999</v>
+        <v>1.4121</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6879</v>
+        <v>-2.0756</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9688</v>
+        <v>1.7426</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8332000000000001</v>
+        <v>0.5296</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1356</v>
+        <v>1.213</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9534</v>
+        <v>1.3674</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4331</v>
+        <v>0.1705</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0989</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.532</v>
+        <v>0.2502</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3869</v>
+        <v>-1.2186</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.1097</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3278</v>
+        <v>0.1274</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3059</v>
+        <v>-1.0847</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9781</v>
+        <v>1.2121</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0791</v>
+        <v>-0.9486</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9417</v>
+        <v>-1.5009</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8626</v>
+        <v>0.5523</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6635</v>
+        <v>0.0202</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4121</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.0756</v>
+        <v>0.6879</v>
       </c>
       <c r="M8" t="n">
-        <v>1.7426</v>
+        <v>-0.9688</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5296</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>1.213</v>
+        <v>-0.1356</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3674</v>
+        <v>1.9534</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5789</v>
+        <v>0.4863</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6657</v>
+        <v>-0.0185</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0868</v>
+        <v>0.5047</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2186</v>
+        <v>-0.3869</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.1097</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8561</v>
+        <v>-0.2022</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1764</v>
+        <v>-2.5498</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3204</v>
+        <v>2.3476</v>
       </c>
       <c r="G9" t="n">
         <v>1.0602</v>
@@ -1156,13 +1156,13 @@
         <v>1.1721</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4001</v>
+        <v>0.2538</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5447</v>
+        <v>0.0819</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1446</v>
+        <v>0.1719</v>
       </c>
       <c r="V9" t="n">
         <v>1.2186</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.93</v>
+        <v>-0.9333</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4541</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3841</v>
+        <v>-1.0028</v>
       </c>
       <c r="G10" t="n">
         <v>-0.546</v>
@@ -1234,13 +1234,13 @@
         <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3974</v>
+        <v>0.3941</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6962</v>
+        <v>0.3117</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2989</v>
+        <v>0.0824</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.132</v>
+        <v>-1.5502</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6239</v>
+        <v>0.9878</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.7559</v>
+        <v>-2.538</v>
       </c>
       <c r="G11" t="n">
         <v>1.2283</v>
@@ -1312,13 +1312,13 @@
         <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.2827</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5915</v>
+        <v>-0.2276</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.273</v>
+        <v>-0.0551</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1052</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>12.0059</v>
+        <v>13.519</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.358600000000001</v>
+        <v>0.1545000000000004</v>
       </c>
       <c r="F12" t="n">
-        <v>13.3646</v>
+        <v>13.3644</v>
       </c>
       <c r="G12" t="n">
         <v>10.1845</v>
@@ -1381,7 +1381,7 @@
         <v>5.387799999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.775557561562891e-16</v>
+        <v>-5.551115123125783e-17</v>
       </c>
       <c r="Q12" t="n">
         <v>-13.6739</v>
@@ -1390,10 +1390,10 @@
         <v>13.6741</v>
       </c>
       <c r="S12" t="n">
-        <v>3.0951</v>
+        <v>4.608</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8244</v>
+        <v>0.6886999999999999</v>
       </c>
       <c r="U12" t="n">
         <v>3.9193</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.3241</v>
+        <v>2.0933</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2088</v>
+        <v>1.0065</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1154</v>
+        <v>1.0868</v>
       </c>
       <c r="G13" t="n">
         <v>0.1342</v>
@@ -1468,13 +1468,13 @@
         <v>0.9767</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5844</v>
+        <v>0.3535</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0689</v>
+        <v>-0.1334</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5155</v>
+        <v>0.4869</v>
       </c>
       <c r="V13" t="n">
         <v>1.6056</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2171</v>
+        <v>1.1418</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1149</v>
+        <v>-0.216</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3319</v>
+        <v>1.3578</v>
       </c>
       <c r="G14" t="n">
         <v>-1.087</v>
@@ -1546,13 +1546,13 @@
         <v>2.1488</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3285</v>
+        <v>-0.4037</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7647</v>
+        <v>-0.8658</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4362</v>
+        <v>0.4621</v>
       </c>
       <c r="V14" t="n">
         <v>2.4373</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1451</v>
+        <v>0.1561</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7202</v>
+        <v>-0.5943000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4249</v>
+        <v>0.7504</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1432</v>
@@ -1624,13 +1624,13 @@
         <v>2.1488</v>
       </c>
       <c r="S15" t="n">
-        <v>1.093</v>
+        <v>0.1039</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1366</v>
+        <v>-0.1779</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0436</v>
+        <v>0.2818</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4903</v>
+        <v>0.0037</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.9935</v>
+        <v>-1.6901</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5032</v>
+        <v>1.6939</v>
       </c>
       <c r="G16" t="n">
         <v>-0.5239</v>
@@ -1702,13 +1702,13 @@
         <v>0.7814</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7478</v>
+        <v>-0.2538</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6657</v>
+        <v>-0.3624</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.082</v>
+        <v>0.1086</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4883</v>
+        <v>-0.9024</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3421</v>
+        <v>-0.8365</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1462</v>
+        <v>-0.0659</v>
       </c>
       <c r="G17" t="n">
         <v>4.0395</v>
@@ -1780,13 +1780,13 @@
         <v>2.5395</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1754</v>
+        <v>-0.5895</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3782</v>
+        <v>-0.8727</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2029</v>
+        <v>0.2832</v>
       </c>
       <c r="V17" t="n">
         <v>-0.0549</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.1078</v>
+        <v>-1.5477</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6088</v>
+        <v>-1.1033</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4989</v>
+        <v>-0.4445</v>
       </c>
       <c r="G18" t="n">
         <v>-2.5623</v>
@@ -1858,13 +1858,13 @@
         <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1082</v>
+        <v>-0.5481</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0289</v>
+        <v>-0.5233</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0793</v>
+        <v>-0.0248</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.524</v>
+        <v>-3.1468</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.6872</v>
+        <v>-2.2827</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8368</v>
+        <v>-0.864</v>
       </c>
       <c r="G19" t="n">
         <v>-1.4315</v>
@@ -1936,13 +1936,13 @@
         <v>0.586</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4831</v>
+        <v>-0.1059</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4237</v>
+        <v>-0.0192</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0595</v>
+        <v>-0.0867</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2186</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. GOMEZ PRIVAT</t>
+          <t>P. BAGUR PONS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.2524</v>
+        <v>-4.4989</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.1926</v>
+        <v>-2.0511</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9402</v>
+        <v>-2.4478</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.6158</v>
+        <v>-3.9943</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8647</v>
+        <v>-1.7288</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.7511</v>
+        <v>-2.2655</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.2464</v>
+        <v>-1.7376</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9568</v>
+        <v>0.1228</v>
       </c>
       <c r="L20" t="n">
-        <v>-3.2896</v>
+        <v>-1.8604</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3694</v>
+        <v>-2.2567</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9079</v>
+        <v>-1.8516</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5385</v>
+        <v>-0.4051</v>
       </c>
       <c r="P20" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5627</v>
+        <v>1.3674</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3318</v>
+        <v>-0.9306</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0305</v>
+        <v>-0.5907</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3014</v>
+        <v>-0.3399</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5545</v>
+        <v>-0.9414</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5545</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. BAGUR PONS</t>
+          <t>R. GOMEZ PRIVAT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.8295</v>
+        <v>-4.631</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3545</v>
+        <v>-5.5971</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.475</v>
+        <v>0.9661</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.9943</v>
+        <v>-4.6158</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7288</v>
+        <v>-1.8647</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.2655</v>
+        <v>-2.7511</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.7376</v>
+        <v>-4.2464</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1228</v>
+        <v>-0.9568</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.8604</v>
+        <v>-3.2896</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.2567</v>
+        <v>-0.3694</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.8516</v>
+        <v>-0.9079</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4051</v>
+        <v>0.5385</v>
       </c>
       <c r="P21" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="Q21" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.0467</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.374</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-0.5545</v>
+      </c>
+      <c r="W21" t="n">
         <v>0</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.3674</v>
-      </c>
-      <c r="S21" t="n">
-        <v>-1.2612</v>
-      </c>
-      <c r="T21" t="n">
-        <v>-0.8941</v>
-      </c>
-      <c r="U21" t="n">
-        <v>-0.3671</v>
-      </c>
-      <c r="V21" t="n">
-        <v>-0.9414</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0.2772</v>
-      </c>
       <c r="X21" t="n">
-        <v>-1.2186</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-12.006</v>
+        <v>-11.3319</v>
       </c>
       <c r="E22" t="n">
         <v>-13.3646</v>
       </c>
       <c r="F22" t="n">
-        <v>1.358700000000001</v>
+        <v>2.0328</v>
       </c>
       <c r="G22" t="n">
         <v>-10.1843</v>
@@ -2143,7 +2143,7 @@
         <v>-2.0223</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.195500000000001</v>
+        <v>-3.1955</v>
       </c>
       <c r="K22" t="n">
         <v>2.1922</v>
@@ -2161,7 +2161,7 @@
         <v>3.3655</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.0001000000000004331</v>
+        <v>-0.0001000000000005441</v>
       </c>
       <c r="Q22" t="n">
         <v>-13.6739</v>
@@ -2170,19 +2170,19 @@
         <v>13.674</v>
       </c>
       <c r="S22" t="n">
-        <v>-3.095</v>
+        <v>-2.4209</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.9193</v>
+        <v>-3.9194</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8245</v>
+        <v>1.4984</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2735</v>
+        <v>1.273499999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>7.424399999999999</v>
+        <v>7.4244</v>
       </c>
       <c r="X22" t="n">
         <v>-6.151</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484228_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484228_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -558,7 +563,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -626,6 +631,11 @@
       </c>
       <c r="X2" t="n">
         <v>-0.5545</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484228_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -636,7 +646,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -704,6 +714,11 @@
       </c>
       <c r="X3" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484228_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -714,7 +729,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -782,17 +797,22 @@
       </c>
       <c r="X4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484228_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. RECIO PIÑOL</t>
+          <t>A. RECIO PINOL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -860,6 +880,11 @@
       </c>
       <c r="X5" t="n">
         <v>0.3869</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484228_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -870,704 +895,745 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7091</v>
+        <v>1.521</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7998</v>
+        <v>1.521</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9093</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7299</v>
+        <v>1.521</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0289</v>
+        <v>0.307</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7009</v>
+        <v>1.214</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0944</v>
+        <v>1.521</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0668</v>
+        <v>0.307</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0276</v>
+        <v>1.214</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3645</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0379</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6733</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8508</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.079</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9298</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.7145</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484228_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4217</v>
+        <v>1.221</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7199</v>
+        <v>1.221</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1416</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0791</v>
+        <v>1.221</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9417</v>
+        <v>0.614</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8626</v>
+        <v>0.607</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6635</v>
+        <v>1.221</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4121</v>
+        <v>0.614</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.0756</v>
+        <v>0.607</v>
       </c>
       <c r="M7" t="n">
-        <v>1.7426</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5296</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.213</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1705</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.07969999999999999</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2502</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484228_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1274</v>
+        <v>0.4217</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0847</v>
+        <v>-1.7199</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2121</v>
+        <v>2.1416</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9486</v>
+        <v>1.0791</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5009</v>
+        <v>1.9417</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5523</v>
+        <v>-0.8626</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0202</v>
+        <v>-0.6635</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6677999999999999</v>
+        <v>1.4121</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6879</v>
+        <v>-2.0756</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9688</v>
+        <v>1.7426</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8332000000000001</v>
+        <v>0.5296</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1356</v>
+        <v>1.213</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9534</v>
+        <v>1.3674</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4863</v>
+        <v>0.1705</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0185</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5047</v>
+        <v>0.2502</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3869</v>
+        <v>-1.2186</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.1097</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484228_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. DEL RIO GASPAR</t>
+          <t>P. CARRION SORIANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2022</v>
+        <v>0.1881</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5498</v>
+        <v>-0.7212</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3476</v>
+        <v>0.9093</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0602</v>
+        <v>-0.7911</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6825</v>
+        <v>-0.2781</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3776</v>
+        <v>-0.513</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0565</v>
+        <v>-0.4266</v>
       </c>
       <c r="K9" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.7598</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0266</v>
+        <v>-1.1863</v>
       </c>
       <c r="M9" t="n">
-        <v>1.0037</v>
+        <v>-0.3645</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5994</v>
+        <v>-1.0379</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4043</v>
+        <v>0.6733</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.7348</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.9069</v>
+        <v>-2.9301</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2538</v>
+        <v>0.8508</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0819</v>
+        <v>-0.079</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1719</v>
+        <v>0.9298</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2186</v>
+        <v>1.4959</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2186</v>
+        <v>2.7145</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484228_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>H. DEL RIO GASPAR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9333</v>
+        <v>-0.2022</v>
       </c>
       <c r="E10" t="n">
-        <v>0.06950000000000001</v>
+        <v>-2.5498</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0028</v>
+        <v>2.3476</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.546</v>
+        <v>1.0602</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7754</v>
+        <v>0.6825</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2294</v>
+        <v>0.3776</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4926</v>
+        <v>0.0565</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5321</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0395</v>
+        <v>-0.0266</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0386</v>
+        <v>1.0037</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3075</v>
+        <v>0.5994</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2688</v>
+        <v>0.4043</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7814</v>
+        <v>-2.7348</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9534</v>
+        <v>-3.9069</v>
       </c>
       <c r="R10" t="n">
         <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3941</v>
+        <v>0.2538</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3117</v>
+        <v>0.0819</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0824</v>
+        <v>0.1719</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="W10" t="n">
         <v>1.2186</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484228_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5502</v>
+        <v>-0.9333</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9878</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.538</v>
+        <v>-1.0028</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2283</v>
+        <v>-0.546</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1215</v>
+        <v>-0.7754</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1068</v>
+        <v>0.2294</v>
       </c>
       <c r="J11" t="n">
-        <v>2.1921</v>
+        <v>0.4926</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0847</v>
+        <v>0.5321</v>
       </c>
       <c r="L11" t="n">
-        <v>1.1074</v>
+        <v>-0.0395</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9638</v>
+        <v>-1.0386</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-1.3075</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.2688</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3907</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R11" t="n">
-        <v>0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2827</v>
+        <v>0.3941</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2276</v>
+        <v>0.3117</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0551</v>
+        <v>0.0824</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1052</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1052</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484228_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. ABELLO GIRVES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>13.519</v>
+        <v>-1.0935</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1545000000000004</v>
+        <v>-2.3057</v>
       </c>
       <c r="F12" t="n">
-        <v>13.3644</v>
+        <v>1.2121</v>
       </c>
       <c r="G12" t="n">
-        <v>10.1845</v>
+        <v>-2.1696</v>
       </c>
       <c r="H12" t="n">
-        <v>8.161899999999999</v>
+        <v>-2.1149</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0224</v>
+        <v>-0.0547</v>
       </c>
       <c r="J12" t="n">
-        <v>6.988700000000001</v>
+        <v>-1.2008</v>
       </c>
       <c r="K12" t="n">
-        <v>10.3542</v>
+        <v>-1.2817</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.365600000000001</v>
+        <v>0.0809</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1958</v>
+        <v>-0.9688</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.1924</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>5.387799999999999</v>
+        <v>-0.1356</v>
       </c>
       <c r="P12" t="n">
-        <v>-5.551115123125783e-17</v>
+        <v>0.9767</v>
       </c>
       <c r="Q12" t="n">
-        <v>-13.6739</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>13.6741</v>
+        <v>1.9534</v>
       </c>
       <c r="S12" t="n">
-        <v>4.608</v>
+        <v>0.4863</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6886999999999999</v>
+        <v>-0.0185</v>
       </c>
       <c r="U12" t="n">
-        <v>3.9193</v>
+        <v>0.5047</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2734</v>
+        <v>-0.3869</v>
       </c>
       <c r="W12" t="n">
-        <v>6.1508</v>
+        <v>-0.1097</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.4244</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484228_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. GASCON TORNE</t>
+          <t>I. ISERN CASES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.0933</v>
+        <v>-1.5502</v>
       </c>
       <c r="E13" t="n">
-        <v>1.0065</v>
+        <v>0.9878</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0868</v>
+        <v>-2.538</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1342</v>
+        <v>1.2283</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6621</v>
+        <v>0.1215</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7963</v>
+        <v>1.1068</v>
       </c>
       <c r="J13" t="n">
-        <v>0.898</v>
+        <v>2.1921</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3709</v>
+        <v>1.0847</v>
       </c>
       <c r="L13" t="n">
-        <v>0.527</v>
+        <v>1.1074</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.7638</v>
+        <v>-0.9638</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.033</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2692</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3535</v>
+        <v>-0.2827</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1334</v>
+        <v>-0.2276</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4869</v>
+        <v>-0.0551</v>
       </c>
       <c r="V13" t="n">
-        <v>1.6056</v>
+        <v>-2.1052</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.3869</v>
+        <v>-2.1052</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484228_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. CORBERA BUSQUETA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1418</v>
+        <v>13.5191</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.216</v>
+        <v>0.1545000000000005</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3578</v>
+        <v>13.3644</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.087</v>
+        <v>10.1845</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.031</v>
+        <v>8.161899999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9439</v>
+        <v>2.0225</v>
       </c>
       <c r="J14" t="n">
-        <v>0.166</v>
+        <v>6.988700000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.5091</v>
+        <v>10.3543</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6751</v>
+        <v>-3.365500000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.253</v>
+        <v>3.1958</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.5219</v>
+        <v>-2.1924</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2688</v>
+        <v>5.387799999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1953</v>
+        <v>2.775557561562891e-16</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9534</v>
+        <v>-13.6739</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1488</v>
+        <v>13.6741</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4037</v>
+        <v>4.608</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8658</v>
+        <v>0.6886999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4621</v>
+        <v>3.9193</v>
       </c>
       <c r="V14" t="n">
-        <v>2.4373</v>
+        <v>-1.2734</v>
       </c>
       <c r="W14" t="n">
-        <v>2.4373</v>
+        <v>6.1508</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
-      </c>
+        <v>-7.424399999999999</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>J. GASCON TORNE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1561</v>
+        <v>2.0933</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5943000000000001</v>
+        <v>1.0065</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7504</v>
+        <v>1.0868</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1432</v>
+        <v>0.1342</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9599</v>
+        <v>-0.6621</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.103</v>
+        <v>0.7963</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7054</v>
+        <v>0.898</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4817</v>
+        <v>0.3709</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.7763</v>
+        <v>0.527</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8485</v>
+        <v>-0.7638</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5219</v>
+        <v>-1.033</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6733</v>
+        <v>0.2692</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1488</v>
+        <v>0.9767</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1039</v>
+        <v>0.3535</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1779</v>
+        <v>-0.1334</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2818</v>
+        <v>0.4869</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.6056</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8317</v>
+        <v>1.2186</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8317</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484228_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ RODRIGUEZ</t>
+          <t>M. CORBERA BUSQUETA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0037</v>
+        <v>1.1418</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.6901</v>
+        <v>-0.216</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6939</v>
+        <v>1.3578</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5239</v>
+        <v>-1.087</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3888</v>
+        <v>-2.031</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.135</v>
+        <v>0.9439</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.3277</v>
+        <v>0.166</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6536</v>
+        <v>-0.5091</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6741</v>
+        <v>0.6751</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8038999999999999</v>
+        <v>-1.253</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2648</v>
+        <v>-1.5219</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5391</v>
+        <v>0.2688</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7814</v>
+        <v>2.1488</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2538</v>
+        <v>-0.4037</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3624</v>
+        <v>-0.8658</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1086</v>
+        <v>0.4621</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484228_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. HERNANDEZ GIMENEZ</t>
+          <t>G. GARCÍA RIERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9024</v>
+        <v>0.614</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8365</v>
+        <v>0.614</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0659</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>4.0395</v>
+        <v>0.614</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6119</v>
+        <v>0.614</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4275</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>5.4322</v>
+        <v>0.614</v>
       </c>
       <c r="K17" t="n">
-        <v>3.5431</v>
+        <v>0.614</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8891</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3927</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.9312</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5385</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-4.2975</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-6.837</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5395</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5895</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8727</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2832</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.441</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484228_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>V. FERNANDEZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5477</v>
+        <v>0.0037</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1033</v>
+        <v>-1.6901</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4445</v>
+        <v>1.6939</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.5623</v>
+        <v>-0.5239</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.2226</v>
+        <v>-0.3888</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6603</v>
+        <v>-0.135</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.7986</v>
+        <v>-1.3277</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.92</v>
+        <v>-0.6536</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1214</v>
+        <v>-0.6741</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7638</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3026</v>
+        <v>0.2648</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5389</v>
+        <v>0.5391</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5481</v>
+        <v>-0.2538</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5233</v>
+        <v>-0.3624</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0248</v>
+        <v>0.1086</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484228_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. ANDUJAR MASCARO</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.1468</v>
+        <v>-0.4579</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2827</v>
+        <v>-1.2082</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.864</v>
+        <v>0.7504</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4315</v>
+        <v>-0.7571</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.8358</v>
+        <v>1.3459</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4043</v>
+        <v>-2.103</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2868</v>
+        <v>0.0914</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.2868</v>
+        <v>2.8677</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-2.7763</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1447</v>
+        <v>-0.8485</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.549</v>
+        <v>-1.5219</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4043</v>
+        <v>0.6733</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>0.586</v>
+        <v>2.1488</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1059</v>
+        <v>0.1039</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0192</v>
+        <v>-0.1779</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0867</v>
+        <v>0.2818</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.8317</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2186</v>
+        <v>-0.8317</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484228_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. BAGUR PONS</t>
+          <t>J. HERNANDEZ GIMENEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.4989</v>
+        <v>-0.9024</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0511</v>
+        <v>-0.8365</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.4478</v>
+        <v>-0.0659</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.9943</v>
+        <v>4.0395</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.7288</v>
+        <v>1.6119</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.2655</v>
+        <v>2.4275</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.7376</v>
+        <v>5.4322</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1228</v>
+        <v>3.5431</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.8604</v>
+        <v>1.8891</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.2567</v>
+        <v>-1.3927</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.8516</v>
+        <v>-1.9312</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4051</v>
+        <v>0.5385</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3674</v>
+        <v>-4.2975</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-6.837</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3674</v>
+        <v>2.5395</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9306</v>
+        <v>-0.5895</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5907</v>
+        <v>-0.8727</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3399</v>
+        <v>0.2832</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9414</v>
+        <v>-0.0549</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2772</v>
+        <v>1.441</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484228_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. GOMEZ PRIVAT</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.631</v>
+        <v>-1.5477</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.5971</v>
+        <v>-1.1033</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9661</v>
+        <v>-0.4445</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.6158</v>
+        <v>-2.5623</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.8647</v>
+        <v>-3.2226</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.7511</v>
+        <v>0.6603</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.2464</v>
+        <v>-1.7986</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9568</v>
+        <v>-1.92</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.2896</v>
+        <v>0.1214</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3694</v>
+        <v>-0.7638</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9079</v>
+        <v>-1.3026</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5385</v>
+        <v>0.5389</v>
       </c>
       <c r="P21" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>1.5627</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0467</v>
+        <v>-0.5481</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.374</v>
+        <v>-0.5233</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3272</v>
+        <v>-0.0248</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5545</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484228_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>L. ANDUJAR MASCARO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,68 +2226,318 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
+        <v>-3.1468</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-2.2827</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.864</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-1.4315</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-1.8358</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.4043</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-1.2868</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-1.2868</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.1447</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.549</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.4043</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-0.1059</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.0192</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.0867</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484228_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>P. BAGUR PONS</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-4.4989</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-2.0511</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-2.4478</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-3.9943</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-1.7288</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-2.2655</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-1.7376</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.1228</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-1.8604</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-2.2567</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-1.8516</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.4051</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.9306</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.5907</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.3399</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-0.9414</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484228_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>R. GOMEZ PRIVAT</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-4.631</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-5.5971</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.9661</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-4.6158</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.8647</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-2.7511</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-4.2464</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.9568</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-3.2896</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.3694</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.9079</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.5385</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.0467</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.374</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.5545</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-0.5545</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484228_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
         <v>-11.3319</v>
       </c>
-      <c r="E22" t="n">
-        <v>-13.3646</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2.0328</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-10.1843</v>
-      </c>
-      <c r="H22" t="n">
+      <c r="E25" t="n">
+        <v>-13.3645</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.032799999999999</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-10.1842</v>
+      </c>
+      <c r="H25" t="n">
         <v>-8.161999999999999</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I25" t="n">
         <v>-2.0223</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J25" t="n">
         <v>-3.1955</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K25" t="n">
         <v>2.1922</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L25" t="n">
         <v>-5.3878</v>
       </c>
-      <c r="M22" t="n">
-        <v>-6.9887</v>
-      </c>
-      <c r="N22" t="n">
+      <c r="M25" t="n">
+        <v>-6.988700000000001</v>
+      </c>
+      <c r="N25" t="n">
         <v>-10.3543</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O25" t="n">
         <v>3.3655</v>
       </c>
-      <c r="P22" t="n">
-        <v>-0.0001000000000005441</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="P25" t="n">
+        <v>-0.0001000000000009882</v>
+      </c>
+      <c r="Q25" t="n">
         <v>-13.6739</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R25" t="n">
         <v>13.674</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S25" t="n">
         <v>-2.4209</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T25" t="n">
         <v>-3.9194</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U25" t="n">
         <v>1.4984</v>
       </c>
-      <c r="V22" t="n">
-        <v>1.273499999999999</v>
-      </c>
-      <c r="W22" t="n">
-        <v>7.4244</v>
-      </c>
-      <c r="X22" t="n">
-        <v>-6.151</v>
-      </c>
+      <c r="V25" t="n">
+        <v>1.2735</v>
+      </c>
+      <c r="W25" t="n">
+        <v>7.424399999999999</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-6.150999999999999</v>
+      </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
